--- a/exports/GLENMARK_full_report.xlsx
+++ b/exports/GLENMARK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.69</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>508.55</v>
+        <v>494.65</v>
       </c>
       <c r="I2" t="n">
         <v>499.0926934101001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.48</v>
+        <v>-5.15</v>
       </c>
       <c r="L2" t="n">
-        <v>3.16</v>
+        <v>5.74</v>
       </c>
       <c r="M2" t="n">
         <v>0.23</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.95</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44643.55208333334</v>
+        <v>44644.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>453.6</v>
+        <v>466.95</v>
       </c>
       <c r="I3" t="n">
         <v>460.6105038501511</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>64</v>
+        <v>64.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
         <v>2.88</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44671.55208333334</v>
+        <v>44672.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>458.1</v>
+        <v>454.15</v>
       </c>
       <c r="I4" t="n">
         <v>457.7199249720869</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9</v>
+        <v>-2.74</v>
       </c>
       <c r="L4" t="n">
         <v>6.08</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.28</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>376</v>
+        <v>380.9</v>
       </c>
       <c r="I5" t="n">
         <v>379.5683910698089</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>17.21</v>
+        <v>16.13</v>
       </c>
       <c r="L5" t="n">
         <v>1.81</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44764.38541666666</v>
+        <v>44764.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>376.8</v>
+        <v>373.1</v>
       </c>
       <c r="I6" t="n">
         <v>373.4656714296966</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.08</v>
+        <v>-2.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="M6" t="n">
         <v>0.9</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>5.43</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44784.38541666666</v>
+        <v>44784.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="I7" t="n">
         <v>383.0685522608396</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.24</v>
+        <v>-3.73</v>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>5.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.3</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>385.9</v>
+        <v>374.9</v>
       </c>
       <c r="I8" t="n">
         <v>376.3666444862315</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.28</v>
+        <v>-3.13</v>
       </c>
       <c r="L8" t="n">
         <v>3.7</v>
@@ -897,7 +992,7 @@
         <v>-0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.31</v>
+        <v>4.38</v>
       </c>
       <c r="O8" t="n">
         <v>3.2</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>386.9</v>
+        <v>390.65</v>
       </c>
       <c r="I9" t="n">
         <v>389.3050609174927</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.2</v>
+        <v>-4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>4.56</v>
+        <v>4.95</v>
       </c>
       <c r="M9" t="n">
         <v>0.53</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>4.69</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44820.38541666666</v>
+        <v>44820.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>378.5</v>
+        <v>372.4</v>
       </c>
       <c r="I10" t="n">
         <v>375.8526097214033</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.11</v>
+        <v>-4.67</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>5.16</v>
       </c>
       <c r="M10" t="n">
         <v>1.18</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.23</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44834.55208333334</v>
+        <v>44837.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>389.55</v>
+        <v>403.45</v>
       </c>
       <c r="I11" t="n">
         <v>391.2245518140086</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.61</v>
+        <v>-8.34</v>
       </c>
       <c r="L11" t="n">
-        <v>6.07</v>
+        <v>9.24</v>
       </c>
       <c r="M11" t="n">
         <v>0.6</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.02</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44883.38541666666</v>
+        <v>44883.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>412.65</v>
+        <v>408.85</v>
       </c>
       <c r="I12" t="n">
         <v>409.3771928766113</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>2.28</v>
+        <v>1.34</v>
       </c>
       <c r="L12" t="n">
         <v>6.54</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.64</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>431.15</v>
+        <v>437.2</v>
       </c>
       <c r="I13" t="n">
         <v>434.8410352914147</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.45</v>
+        <v>-6.93</v>
       </c>
       <c r="L13" t="n">
-        <v>5.98</v>
+        <v>8.6</v>
       </c>
       <c r="M13" t="n">
         <v>0.57</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.24</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>421.35</v>
+        <v>418</v>
       </c>
       <c r="I14" t="n">
         <v>418.4354146623423</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.63</v>
+        <v>-4.39</v>
       </c>
       <c r="L14" t="n">
         <v>5.03</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.94</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>409.6</v>
+        <v>439.65</v>
       </c>
       <c r="I15" t="n">
         <v>430.9219550417871</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>2.01</v>
+        <v>-5.18</v>
       </c>
       <c r="L15" t="n">
-        <v>0.92</v>
+        <v>5.51</v>
       </c>
       <c r="M15" t="n">
         <v>0.74</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="O15" t="n">
         <v>-4.03</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.91</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>412.75</v>
+        <v>402.95</v>
       </c>
       <c r="I16" t="n">
         <v>410.9143853323314</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.12</v>
+        <v>-8.35</v>
       </c>
       <c r="L16" t="n">
-        <v>6.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>1.71</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>3.21</v>
       </c>
       <c r="O16" t="n">
         <v>7.91</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.97</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>386.2</v>
+        <v>398.9</v>
       </c>
       <c r="I17" t="n">
         <v>396.6690290301255</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>4.16</v>
+        <v>1.01</v>
       </c>
       <c r="L17" t="n">
         <v>2.75</v>
@@ -1410,7 +1613,7 @@
         <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>2.64</v>
+        <v>3.47</v>
       </c>
       <c r="O17" t="n">
         <v>-3.21</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.52</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44987.38541666666</v>
+        <v>44987.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>423.45</v>
+        <v>419</v>
       </c>
       <c r="I18" t="n">
         <v>423.1507844017243</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>6.15</v>
+        <v>5.04</v>
       </c>
       <c r="L18" t="n">
         <v>3.17</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>5.59</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45001.55208333334</v>
+        <v>45002.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>432.9</v>
+        <v>440.35</v>
       </c>
       <c r="I19" t="n">
         <v>436.015034450331</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.32</v>
+        <v>-5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>3.72</v>
+        <v>5.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9</v>
+        <v>1.64</v>
       </c>
       <c r="N19" t="n">
         <v>3.08</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.23</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>642.05</v>
+        <v>626</v>
       </c>
       <c r="I20" t="n">
         <v>629.150473712769</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>96.16666666666667</v>
+        <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>45.8</v>
+        <v>42.16</v>
       </c>
       <c r="L20" t="n">
         <v>3.72</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.8</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45104.55208333334</v>
+        <v>45105.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>655</v>
+        <v>667.25</v>
       </c>
       <c r="I21" t="n">
         <v>657.1931551569504</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.63</v>
+        <v>-6.59</v>
       </c>
       <c r="L21" t="n">
         <v>7.28</v>
       </c>
       <c r="M21" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="N21" t="n">
-        <v>2.34</v>
+        <v>3.51</v>
       </c>
       <c r="O21" t="n">
         <v>-2.09</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>5.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>795.65</v>
+        <v>785</v>
       </c>
       <c r="I22" t="n">
         <v>785.9568446773192</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K22" t="n">
-        <v>19.24</v>
+        <v>17.65</v>
       </c>
       <c r="L22" t="n">
         <v>2.94</v>
       </c>
       <c r="M22" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="N22" t="n">
         <v>3.83</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45174.38541666666</v>
+        <v>45174.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>774.4</v>
+        <v>795.5</v>
       </c>
       <c r="I23" t="n">
         <v>777.9937796437239</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.35</v>
+        <v>-1.34</v>
       </c>
       <c r="L23" t="n">
         <v>2.47</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.58</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>831.95</v>
+        <v>804.4</v>
       </c>
       <c r="I24" t="n">
         <v>815.3577342742236</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>4.58</v>
+        <v>1.12</v>
       </c>
       <c r="L24" t="n">
         <v>3.05</v>
       </c>
       <c r="M24" t="n">
-        <v>0.16</v>
+        <v>3.24</v>
       </c>
       <c r="N24" t="n">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="O24" t="n">
         <v>4.23</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>8.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45197.55208333334</v>
+        <v>45198.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>778.25</v>
+        <v>850.15</v>
       </c>
       <c r="I25" t="n">
         <v>830.5311641940531</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>3.25</v>
+        <v>-5.69</v>
       </c>
       <c r="L25" t="n">
-        <v>3.17</v>
+        <v>6.08</v>
       </c>
       <c r="M25" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="N25" t="n">
-        <v>1.78</v>
+        <v>9.84</v>
       </c>
       <c r="O25" t="n">
         <v>-3.47</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.23</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45208.38541666666</v>
+        <v>45208.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>785.45</v>
+        <v>783.45</v>
       </c>
       <c r="I26" t="n">
         <v>785.2153063025354</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.61</v>
+        <v>-7.85</v>
       </c>
       <c r="L26" t="n">
         <v>8.08</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.63</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45238.38541666666</v>
+        <v>45238.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>778.35</v>
+        <v>788.5</v>
       </c>
       <c r="I27" t="n">
         <v>780.6875315838735</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="L27" t="n">
         <v>4.03</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>5.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45242.76041666666</v>
+        <v>45243.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>767</v>
+        <v>725.95</v>
       </c>
       <c r="I28" t="n">
         <v>741.8791344172813</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4.208333333333333</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.73</v>
+        <v>-7.93</v>
       </c>
       <c r="L28" t="n">
-        <v>4.72</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
         <v>1.59</v>
       </c>
       <c r="N28" t="n">
-        <v>1.19</v>
+        <v>5.62</v>
       </c>
       <c r="O28" t="n">
         <v>3.55</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45247.38541666666</v>
+        <v>45247.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>773.1</v>
+        <v>775</v>
       </c>
       <c r="I29" t="n">
         <v>774.4188366761456</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.49</v>
+        <v>-6.76</v>
       </c>
       <c r="L29" t="n">
         <v>7.91</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.35</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>870.8</v>
+        <v>857.3</v>
       </c>
       <c r="I30" t="n">
         <v>860.7734567175182</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>66.83333333333333</v>
+        <v>67</v>
       </c>
       <c r="K30" t="n">
-        <v>12.36</v>
+        <v>10.62</v>
       </c>
       <c r="L30" t="n">
         <v>1.81</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.93</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>818.05</v>
+        <v>881.25</v>
       </c>
       <c r="I31" t="n">
         <v>854.6926235937296</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>4.58</v>
+        <v>-2.79</v>
       </c>
       <c r="L31" t="n">
         <v>7.63</v>
@@ -2208,7 +2579,7 @@
         <v>1.37</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>6.22</v>
       </c>
       <c r="O31" t="n">
         <v>-1.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.16</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>904.85</v>
+        <v>899.3</v>
       </c>
       <c r="I32" t="n">
         <v>902.7854416820396</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>2.68</v>
+        <v>2.05</v>
       </c>
       <c r="L32" t="n">
         <v>6.72</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.98</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>956</v>
+        <v>977.75</v>
       </c>
       <c r="I33" t="n">
         <v>971.0556787911725</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.3</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>7.79</v>
+        <v>9.08</v>
       </c>
       <c r="M33" t="n">
         <v>0.84</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.21</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1040</v>
+        <v>1003</v>
       </c>
       <c r="I34" t="n">
         <v>1032.205986460787</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>6.37</v>
+        <v>2.58</v>
       </c>
       <c r="L34" t="n">
         <v>1.91</v>
@@ -2379,7 +2786,7 @@
         <v>1.94</v>
       </c>
       <c r="N34" t="n">
-        <v>1.51</v>
+        <v>2.61</v>
       </c>
       <c r="O34" t="n">
         <v>3.02</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45436.55208333334</v>
+        <v>45439.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1031.55</v>
+        <v>1112</v>
       </c>
       <c r="I35" t="n">
         <v>1060.322856919364</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.85</v>
+        <v>-10.87</v>
       </c>
       <c r="L35" t="n">
-        <v>4.99</v>
+        <v>12.05</v>
       </c>
       <c r="M35" t="n">
         <v>0.61</v>
       </c>
       <c r="N35" t="n">
-        <v>2.61</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O35" t="n">
         <v>-2.61</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1717.1</v>
+        <v>1653.5</v>
       </c>
       <c r="I36" t="n">
         <v>1684.169195090238</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>113.1666666666667</v>
+        <v>114</v>
       </c>
       <c r="K36" t="n">
-        <v>54.42</v>
+        <v>48.7</v>
       </c>
       <c r="L36" t="n">
         <v>7.26</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.68</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45573.38541666666</v>
+        <v>45573.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1718.95</v>
+        <v>1739</v>
       </c>
       <c r="I37" t="n">
         <v>1724.594647741165</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.96</v>
+        <v>-5.17</v>
       </c>
       <c r="L37" t="n">
         <v>6.68</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>6.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45582.55208333334</v>
+        <v>45583.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1734.1</v>
+        <v>1722.25</v>
       </c>
       <c r="I38" t="n">
         <v>1727.068514415603</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.28</v>
+        <v>-0.96</v>
       </c>
       <c r="L38" t="n">
         <v>1.37</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="N38" t="n">
         <v>2.41</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>5.9</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1725.1</v>
+        <v>1757.6</v>
       </c>
       <c r="I39" t="n">
         <v>1757.445735938327</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.17</v>
+        <v>-2.05</v>
       </c>
       <c r="L39" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="M39" t="n">
         <v>0.48</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.75</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1654.1</v>
+        <v>1649.5</v>
       </c>
       <c r="I40" t="n">
         <v>1649.885105188809</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.89</v>
+        <v>-6.15</v>
       </c>
       <c r="L40" t="n">
         <v>6.46</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45652.55208333334</v>
+        <v>45653.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1544</v>
+        <v>1593</v>
       </c>
       <c r="I41" t="n">
         <v>1572.377230493624</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K41" t="n">
-        <v>6.4</v>
+        <v>3.43</v>
       </c>
       <c r="L41" t="n">
         <v>2.12</v>
@@ -2778,7 +3269,7 @@
         <v>1.46</v>
       </c>
       <c r="N41" t="n">
-        <v>2.29</v>
+        <v>2.98</v>
       </c>
       <c r="O41" t="n">
         <v>-0.98</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.15</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1589.9</v>
+        <v>1552.4</v>
       </c>
       <c r="I42" t="n">
         <v>1572.565162022303</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.19</v>
+        <v>-2.55</v>
       </c>
       <c r="L42" t="n">
         <v>3.31</v>
       </c>
       <c r="M42" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>3.03</v>
       </c>
       <c r="O42" t="n">
         <v>2.98</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.23</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45693.38541666666</v>
+        <v>45693.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1477.95</v>
+        <v>1498.85</v>
       </c>
       <c r="I43" t="n">
         <v>1485.560417574168</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="L43" t="n">
         <v>2.84</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.98</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1503.8</v>
+        <v>1433.6</v>
       </c>
       <c r="I44" t="n">
         <v>1445.999892759134</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>0.33</v>
+        <v>-4.35</v>
       </c>
       <c r="L44" t="n">
-        <v>1.65</v>
+        <v>4.79</v>
       </c>
       <c r="M44" t="n">
         <v>0.73</v>
       </c>
       <c r="N44" t="n">
-        <v>2.35</v>
+        <v>3.32</v>
       </c>
       <c r="O44" t="n">
         <v>3.38</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.02</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1330.05</v>
+        <v>1384.4</v>
       </c>
       <c r="I45" t="n">
         <v>1379.189224271752</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K45" t="n">
-        <v>7.22</v>
+        <v>3.43</v>
       </c>
       <c r="L45" t="n">
         <v>5.33</v>
@@ -3006,7 +3545,7 @@
         <v>1.47</v>
       </c>
       <c r="N45" t="n">
-        <v>4.29</v>
+        <v>4.51</v>
       </c>
       <c r="O45" t="n">
         <v>-3.32</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.57</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1500</v>
+        <v>1452.45</v>
       </c>
       <c r="I46" t="n">
         <v>1453.046299508699</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K46" t="n">
-        <v>8.35</v>
+        <v>4.92</v>
       </c>
       <c r="L46" t="n">
         <v>4.55</v>
       </c>
       <c r="M46" t="n">
-        <v>1.12</v>
+        <v>9.33</v>
       </c>
       <c r="N46" t="n">
-        <v>2.64</v>
+        <v>3.77</v>
       </c>
       <c r="O46" t="n">
         <v>4.51</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1418</v>
+        <v>1445.9</v>
       </c>
       <c r="I47" t="n">
         <v>1442.796317691668</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K47" t="n">
-        <v>2.37</v>
+        <v>0.45</v>
       </c>
       <c r="L47" t="n">
         <v>1.68</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.57</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2069.9</v>
+        <v>2046</v>
       </c>
       <c r="I48" t="n">
         <v>2060.912366311517</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K48" t="n">
-        <v>43.16</v>
+        <v>41.5</v>
       </c>
       <c r="L48" t="n">
         <v>5.25</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.95</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45903.38541666666</v>
+        <v>45903.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1991.5</v>
+        <v>2007</v>
       </c>
       <c r="I49" t="n">
         <v>1999.576061121261</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>2.66</v>
+        <v>1.91</v>
       </c>
       <c r="L49" t="n">
         <v>1.55</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.43</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>2092.5</v>
+        <v>2036.9</v>
       </c>
       <c r="I50" t="n">
         <v>2039.338904163598</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>4.26</v>
+        <v>1.49</v>
       </c>
       <c r="L50" t="n">
         <v>1.37</v>
@@ -3291,7 +3890,7 @@
         <v>0.25</v>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>3.37</v>
       </c>
       <c r="O50" t="n">
         <v>4.53</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1890</v>
+        <v>1894.9</v>
       </c>
       <c r="I51" t="n">
         <v>1894.10961192739</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>7.21</v>
+        <v>6.97</v>
       </c>
       <c r="L51" t="n">
         <v>3.26</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.33</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1821</v>
+        <v>1808.3</v>
       </c>
       <c r="I52" t="n">
         <v>1812.85863498469</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.9</v>
+        <v>-4.57</v>
       </c>
       <c r="L52" t="n">
-        <v>4.37</v>
+        <v>4.74</v>
       </c>
       <c r="M52" t="n">
         <v>0.05</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.42</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45973.55208333334</v>
+        <v>45974.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1850</v>
+        <v>1906</v>
       </c>
       <c r="I53" t="n">
         <v>1902.136459818591</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.31</v>
+        <v>-5.4</v>
       </c>
       <c r="L53" t="n">
-        <v>2.91</v>
+        <v>6.12</v>
       </c>
       <c r="M53" t="n">
-        <v>0.17</v>
+        <v>0.65</v>
       </c>
       <c r="N53" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O53" t="n">
         <v>-1.98</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.55</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>2038.6</v>
+        <v>2002.6</v>
       </c>
       <c r="I54" t="n">
         <v>2026.462016510111</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>6.96</v>
+        <v>5.07</v>
       </c>
       <c r="L54" t="n">
         <v>5.04</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.98</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46065.38541666666</v>
+        <v>46065.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>2034.1</v>
+        <v>2036.3</v>
       </c>
       <c r="I55" t="n">
         <v>2034.544237453616</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.57</v>
+        <v>-1.68</v>
       </c>
       <c r="L55" t="n">
         <v>2</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.53</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2134.1</v>
+        <v>2045.7</v>
       </c>
       <c r="I56" t="n">
         <v>2047.543331129795</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>4.8</v>
+        <v>0.46</v>
       </c>
       <c r="L56" t="n">
         <v>2.37</v>
@@ -3633,7 +4304,7 @@
         <v>1.7</v>
       </c>
       <c r="N56" t="n">
-        <v>2.12</v>
+        <v>4.53</v>
       </c>
       <c r="O56" t="n">
         <v>1.03</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.48</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46090.55208333334</v>
+        <v>46091.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2119</v>
+        <v>2216.6</v>
       </c>
       <c r="I57" t="n">
         <v>2168.556890445741</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.58</v>
+        <v>-8.35</v>
       </c>
       <c r="L57" t="n">
-        <v>4.51</v>
+        <v>8.75</v>
       </c>
       <c r="M57" t="n">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="N57" t="n">
-        <v>3.42</v>
+        <v>5.62</v>
       </c>
       <c r="O57" t="n">
         <v>-4.53</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46099.55208333334</v>
+        <v>46100.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2188.9</v>
+        <v>2113.5</v>
       </c>
       <c r="I58" t="n">
         <v>2135.122356407492</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.25</v>
+        <v>-4.65</v>
       </c>
       <c r="L58" t="n">
-        <v>3.89</v>
+        <v>4.7</v>
       </c>
       <c r="M58" t="n">
         <v>0.79</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2205</v>
+        <v>2244.7</v>
       </c>
       <c r="I59" t="n">
         <v>2207.312662275544</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.33</v>
+        <v>-6.21</v>
       </c>
       <c r="L59" t="n">
-        <v>5.91</v>
+        <v>6.61</v>
       </c>
       <c r="M59" t="n">
         <v>2.83</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.88</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>2287.6</v>
+        <v>2267.9</v>
       </c>
       <c r="I60" t="n">
         <v>2285.71496738825</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="L60" t="n">
         <v>1.78</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.16</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46161.38541666666</v>
+        <v>46161.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>2385</v>
+        <v>2409</v>
       </c>
       <c r="I61" t="n">
         <v>2407.637062591572</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.16</v>
+        <v>-6.22</v>
       </c>
       <c r="L61" t="n">
-        <v>5.56</v>
+        <v>6.42</v>
       </c>
       <c r="M61" t="n">
         <v>0.61</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46163.55208333334</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2388</v>
+        <v>2251.9</v>
       </c>
       <c r="I62" t="n">
         <v>2280.231019263599</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.87</v>
+        <v>-6.52</v>
       </c>
       <c r="L62" t="n">
-        <v>1.62</v>
+        <v>7.58</v>
       </c>
       <c r="M62" t="n">
         <v>-0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.62</v>
+        <v>5.75</v>
       </c>
       <c r="O62" t="n">
         <v>2.38</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2215</v>
+        <v>2262.7</v>
       </c>
       <c r="I63" t="n">
         <v>2253.703023614696</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K63" t="n">
-        <v>1.64</v>
+        <v>-0.48</v>
       </c>
       <c r="L63" t="n">
         <v>7.19</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.97</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>2201</v>
+        <v>2194.4</v>
       </c>
       <c r="I64" t="n">
         <v>2200.030050959622</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.73</v>
+        <v>-3.02</v>
       </c>
       <c r="L64" t="n">
         <v>4.27</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.22</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46241.38541666666</v>
+        <v>46241.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>2269.2</v>
+        <v>2285</v>
       </c>
       <c r="I65" t="n">
         <v>2281.531559098091</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.41</v>
+        <v>-4.13</v>
       </c>
       <c r="L65" t="n">
         <v>4.36</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>4.81</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46252.55208333334</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>2315</v>
+        <v>2234.2</v>
       </c>
       <c r="I66" t="n">
         <v>2236.825591730075</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>1.31</v>
+        <v>-2.22</v>
       </c>
       <c r="L66" t="n">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
       <c r="M66" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="N66" t="n">
-        <v>1.23</v>
+        <v>2.83</v>
       </c>
       <c r="O66" t="n">
         <v>1.33</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>5.92</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46254.38541666666</v>
+        <v>46254.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>2317.9</v>
+        <v>2339.1</v>
       </c>
       <c r="I67" t="n">
         <v>2337.68652615484</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.75</v>
+        <v>-4.7</v>
       </c>
       <c r="L67" t="n">
-        <v>4.11</v>
+        <v>4.82</v>
       </c>
       <c r="M67" t="n">
         <v>0.64</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>5.27</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>2378.9</v>
+        <v>2375</v>
       </c>
       <c r="I68" t="n">
         <v>2376.947005983477</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K68" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="L68" t="n">
         <v>1.87</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.18</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46288.38541666666</v>
+        <v>46288.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>2471.4</v>
+        <v>2475</v>
       </c>
       <c r="I69" t="n">
         <v>2474.238381040678</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.06</v>
+        <v>-4.21</v>
       </c>
       <c r="L69" t="n">
         <v>4.53</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>3.86</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>2382</v>
+        <v>2329.1</v>
       </c>
       <c r="I70" t="n">
         <v>2379.392086661689</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.76</v>
+        <v>-5.89</v>
       </c>
       <c r="L70" t="n">
-        <v>4.42</v>
+        <v>5.94</v>
       </c>
       <c r="M70" t="n">
         <v>0.74</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>40</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113.2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.66</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.11</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.13</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.42</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.03</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.72</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.08</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.07</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.19</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.24</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
